--- a/Data/Control_Database.xlsx
+++ b/Data/Control_Database.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/Thesis/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB61E8A2-EBC3-6040-98DC-1202E1E2DC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7082DDAD-B45B-7D4E-9DD4-806BDE47EF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
+    <workbookView xWindow="13780" yWindow="1560" windowWidth="13620" windowHeight="16940" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>BRAND DATABASE</t>
   </si>
@@ -89,24 +89,9 @@
     <t>Wrangler</t>
   </si>
   <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Carhartt</t>
-  </si>
-  <si>
-    <t>Dickies</t>
-  </si>
-  <si>
-    <t>Ralph Lauren</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tommy Hilfiger </t>
   </si>
   <si>
-    <t>Clavin Klein</t>
-  </si>
-  <si>
     <t>Michael Kors</t>
   </si>
   <si>
@@ -122,9 +107,6 @@
     <t>Victoria's Secret</t>
   </si>
   <si>
-    <t>SKIMS</t>
-  </si>
-  <si>
     <t>Forever 21</t>
   </si>
   <si>
@@ -140,12 +122,6 @@
     <t>Marc Jacobs</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom Ford </t>
-  </si>
-  <si>
-    <t>The Row</t>
-  </si>
-  <si>
     <t>Urban Outfitters</t>
   </si>
   <si>
@@ -156,13 +132,28 @@
   </si>
   <si>
     <t xml:space="preserve">LL Bean </t>
+  </si>
+  <si>
+    <t>Ralph Lauren Corporation</t>
+  </si>
+  <si>
+    <t>Kate Spade &amp; Co</t>
+  </si>
+  <si>
+    <t>The North Face</t>
+  </si>
+  <si>
+    <t>Calvin Klein</t>
+  </si>
+  <si>
+    <t>Tom Ford</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -193,6 +184,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -214,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -225,6 +222,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,8 +557,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF1633F-6EA6-034C-A39E-6A5F71E344D2}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -589,42 +590,42 @@
       <c r="B4" s="5">
         <v>49.83383979741437</v>
       </c>
-      <c r="C4" s="5">
-        <v>54.664841198336532</v>
+      <c r="C4" s="6">
+        <v>47</v>
       </c>
       <c r="D4" s="5">
-        <f t="shared" ref="D4:D38" si="0">(B4-C4)+100</f>
-        <v>95.168998599077838</v>
+        <f t="shared" ref="D4:D15" si="0">(B4-C4)+100</f>
+        <v>102.83383979741437</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="5">
-        <v>53.533759829401575</v>
-      </c>
-      <c r="C5" s="5">
-        <v>67.283225516853889</v>
+        <v>54.234559509529525</v>
+      </c>
+      <c r="C5" s="6">
+        <v>34</v>
       </c>
       <c r="D5" s="5">
-        <f t="shared" si="0"/>
-        <v>86.250534312547686</v>
+        <f>(B5-C5)+100</f>
+        <v>120.23455950952953</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="5">
-        <v>54.234559509529525</v>
-      </c>
-      <c r="C6" s="5">
-        <v>39.005627517921248</v>
+        <v>53.533759829401575</v>
+      </c>
+      <c r="C6" s="6">
+        <v>66</v>
       </c>
       <c r="D6" s="5">
-        <f t="shared" si="0"/>
-        <v>115.22893199160828</v>
+        <f>(B6-C6)+100</f>
+        <v>87.533759829401575</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -634,12 +635,12 @@
       <c r="B7" s="5">
         <v>39.60035985605758</v>
       </c>
-      <c r="C7" s="5">
-        <v>57.32795972297783</v>
+      <c r="C7" s="6">
+        <v>46</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="0"/>
-        <v>82.272400133079742</v>
+        <v>93.60035985605758</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -649,12 +650,12 @@
       <c r="B8" s="5">
         <v>49.20095961615354</v>
       </c>
-      <c r="C8" s="5">
-        <v>53.396902838943149</v>
+      <c r="C8" s="6">
+        <v>55</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" si="0"/>
-        <v>95.804056777210391</v>
+        <v>94.20095961615354</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -664,12 +665,12 @@
       <c r="B9" s="5">
         <v>52.352872763937903</v>
       </c>
-      <c r="C9" s="5">
-        <v>99.968396579040302</v>
+      <c r="C9" s="6">
+        <v>100</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="0"/>
-        <v>52.384476184897601</v>
+        <v>52.352872763937903</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -679,12 +680,12 @@
       <c r="B10" s="5">
         <v>54.610314522371297</v>
       </c>
-      <c r="C10" s="5">
-        <v>58.695881197943336</v>
+      <c r="C10" s="6">
+        <v>55</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="0"/>
-        <v>95.914433324427961</v>
+        <v>99.610314522371297</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -694,12 +695,12 @@
       <c r="B11" s="5">
         <v>66.98073034217856</v>
       </c>
-      <c r="C11" s="5">
-        <v>68.496590174873091</v>
+      <c r="C11" s="6">
+        <v>71</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="0"/>
-        <v>98.484140167305469</v>
+        <v>95.98073034217856</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -709,12 +710,12 @@
       <c r="B12" s="5">
         <v>65.643346109831924</v>
       </c>
-      <c r="C12" s="5">
-        <v>61.165080374149582</v>
+      <c r="C12" s="6">
+        <v>67</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="0"/>
-        <v>104.47826573568234</v>
+        <v>98.643346109831924</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -724,12 +725,12 @@
       <c r="B13" s="5">
         <v>59.415690964993317</v>
       </c>
-      <c r="C13" s="5">
-        <v>46.628625745439919</v>
+      <c r="C13" s="6">
+        <v>50</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="0"/>
-        <v>112.7870652195534</v>
+        <v>109.41569096499332</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -739,12 +740,12 @@
       <c r="B14" s="5">
         <v>53.642262900429138</v>
       </c>
-      <c r="C14" s="5">
-        <v>60.276696515075933</v>
+      <c r="C14" s="6">
+        <v>59</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="0"/>
-        <v>93.365566385353205</v>
+        <v>94.642262900429131</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -754,357 +755,312 @@
       <c r="B15" s="5">
         <v>60.395596306931772</v>
       </c>
-      <c r="C15" s="5">
-        <v>43.200866176278666</v>
+      <c r="C15" s="6">
+        <v>34</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="0"/>
-        <v>117.19473013065311</v>
+        <v>126.39559630693176</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5">
-        <v>62.595596306931775</v>
-      </c>
-      <c r="C16" s="5">
-        <v>39.005627517921248</v>
+        <v>57.96405074333903</v>
+      </c>
+      <c r="C16" s="6">
+        <v>62</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="0"/>
-        <v>123.58996878901053</v>
+        <f t="shared" ref="D16:D35" si="1">(B16-C16)+100</f>
+        <v>95.96405074333903</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>41.380383825672503</v>
-      </c>
-      <c r="C17" s="5">
-        <v>33.597024201544627</v>
+        <v>49.370522432274925</v>
+      </c>
+      <c r="C17" s="6">
+        <v>53</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="0"/>
-        <v>107.78335962412788</v>
+        <f t="shared" si="1"/>
+        <v>96.370522432274925</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B18" s="5">
-        <v>57.370175915768868</v>
-      </c>
-      <c r="C18" s="5">
-        <v>49.526755166678583</v>
+        <v>56.986668968776129</v>
+      </c>
+      <c r="C18" s="6">
+        <v>49</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="0"/>
-        <v>107.84342074909028</v>
+        <f t="shared" si="1"/>
+        <v>107.98666896877613</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5">
-        <v>57.96405074333903</v>
-      </c>
-      <c r="C19" s="5">
-        <v>61.45211842172592</v>
+        <v>57.911007555383392</v>
+      </c>
+      <c r="C19" s="6">
+        <v>44</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="0"/>
-        <v>96.511932321613102</v>
+        <f t="shared" si="1"/>
+        <v>113.91100755538339</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5">
-        <v>49.370522432274925</v>
-      </c>
-      <c r="C20" s="5">
-        <v>67.283225516853889</v>
+        <v>48.923577841590635</v>
+      </c>
+      <c r="C20" s="6">
+        <v>57</v>
       </c>
       <c r="D20" s="5">
-        <f t="shared" si="0"/>
-        <v>82.087296915421035</v>
+        <f t="shared" si="1"/>
+        <v>91.923577841590628</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B21" s="5">
-        <v>56.986668968776129</v>
-      </c>
-      <c r="C21" s="5">
-        <v>67.283225516853889</v>
+        <v>63</v>
+      </c>
+      <c r="C21" s="6">
+        <v>24</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="0"/>
-        <v>89.70344345192224</v>
+        <f t="shared" si="1"/>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B22" s="5">
-        <v>57.911007555383392</v>
-      </c>
-      <c r="C22" s="5">
-        <v>58.363118052216464</v>
+        <v>61.593346109831927</v>
+      </c>
+      <c r="C22" s="6">
+        <v>32</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" si="0"/>
-        <v>99.547889503166928</v>
+        <f t="shared" si="1"/>
+        <v>129.59334610983194</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5">
-        <v>48.923577841590635</v>
-      </c>
-      <c r="C23" s="5">
-        <v>56.604769528049189</v>
+        <v>46.350059976009597</v>
+      </c>
+      <c r="C23" s="6">
+        <v>47</v>
       </c>
       <c r="D23" s="5">
-        <f t="shared" si="0"/>
-        <v>92.318808313541439</v>
+        <f t="shared" si="1"/>
+        <v>99.350059976009589</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5">
-        <v>61.593346109831927</v>
-      </c>
-      <c r="C24" s="5">
-        <v>42.433387087082508</v>
+        <v>41.712159841945578</v>
+      </c>
+      <c r="C24" s="6">
+        <v>59</v>
       </c>
       <c r="D24" s="5">
-        <f t="shared" si="0"/>
-        <v>119.15995902274942</v>
+        <f t="shared" si="1"/>
+        <v>82.712159841945578</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5">
-        <v>46.350059976009597</v>
-      </c>
-      <c r="C25" s="5">
-        <v>58.363118052216464</v>
+        <v>77.485759813721572</v>
+      </c>
+      <c r="C25" s="6">
+        <v>48</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="0"/>
-        <v>87.986941923793125</v>
+        <f t="shared" si="1"/>
+        <v>129.48575981372159</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5">
-        <v>41.712159841945578</v>
-      </c>
-      <c r="C26" s="5">
-        <v>60.276696515075933</v>
+        <v>23.791959882713581</v>
+      </c>
+      <c r="C26" s="6">
+        <v>61</v>
       </c>
       <c r="D26" s="5">
-        <f t="shared" si="0"/>
-        <v>81.435463326869638</v>
+        <f t="shared" si="1"/>
+        <v>62.791959882713584</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5">
-        <v>77.485759813721572</v>
-      </c>
-      <c r="C27" s="5">
-        <v>20.565422657649339</v>
+        <v>47.849323850226448</v>
+      </c>
+      <c r="C27" s="6">
+        <v>32</v>
       </c>
       <c r="D27" s="5">
-        <f t="shared" si="0"/>
-        <v>156.92033715607224</v>
+        <f t="shared" si="1"/>
+        <v>115.84932385022645</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5">
-        <v>23.791959882713581</v>
-      </c>
-      <c r="C28" s="5">
-        <v>39.005627517921248</v>
+        <v>60.95</v>
+      </c>
+      <c r="C28" s="6">
+        <v>56</v>
       </c>
       <c r="D28" s="5">
-        <f t="shared" si="0"/>
-        <v>84.786332364792329</v>
+        <f t="shared" si="1"/>
+        <v>104.95</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" s="5">
-        <v>47.849323850226448</v>
-      </c>
-      <c r="C29" s="5">
-        <v>33.597024201544627</v>
+        <v>65.290591735576129</v>
+      </c>
+      <c r="C29" s="6">
+        <v>29</v>
       </c>
       <c r="D29" s="5">
-        <f t="shared" si="0"/>
-        <v>114.25229964868183</v>
+        <f t="shared" si="1"/>
+        <v>136.29059173557613</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B30" s="5">
-        <v>60.95</v>
-      </c>
-      <c r="C30" s="5">
-        <v>46.628625745439919</v>
+        <v>51.751839194997913</v>
+      </c>
+      <c r="C30" s="6">
+        <v>13</v>
       </c>
       <c r="D30" s="5">
-        <f t="shared" si="0"/>
-        <v>114.32137425456008</v>
+        <f t="shared" si="1"/>
+        <v>138.7518391949979</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5">
-        <v>65.290591735576129</v>
-      </c>
-      <c r="C31" s="5">
-        <v>33.597024201544627</v>
+        <v>37.600733828705188</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0</v>
       </c>
       <c r="D31" s="5">
-        <f t="shared" si="0"/>
-        <v>131.6935675340315</v>
+        <f t="shared" si="1"/>
+        <v>137.60073382870519</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B32" s="5">
-        <v>51.751839194997913</v>
-      </c>
-      <c r="C32" s="5">
-        <v>25.97402597402596</v>
+        <v>40.300959616153534</v>
+      </c>
+      <c r="C32" s="6">
+        <v>25</v>
       </c>
       <c r="D32" s="5">
-        <f t="shared" si="0"/>
-        <v>125.77781322097195</v>
+        <f t="shared" si="1"/>
+        <v>115.30095961615353</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B33" s="5">
-        <v>37.600733828705188</v>
-      </c>
-      <c r="C33" s="5">
-        <v>25.97402597402596</v>
+        <v>40.930159700825556</v>
+      </c>
+      <c r="C33" s="6">
+        <v>39</v>
       </c>
       <c r="D33" s="5">
-        <f t="shared" si="0"/>
-        <v>111.62670785467922</v>
+        <f t="shared" si="1"/>
+        <v>101.93015970082556</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B34" s="5">
-        <v>50.251318068351338</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-8.9177113764626073E-2</v>
+        <v>52.850453128973712</v>
+      </c>
+      <c r="C34" s="6">
+        <v>40</v>
       </c>
       <c r="D34" s="5">
-        <f t="shared" si="0"/>
-        <v>150.34049518211597</v>
+        <f t="shared" si="1"/>
+        <v>112.85045312897371</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B35" s="5">
-        <v>40.300959616153534</v>
-      </c>
-      <c r="C35" s="5">
-        <v>56.969841715792171</v>
+        <v>45.450453128973713</v>
+      </c>
+      <c r="C35" s="6">
+        <v>32</v>
       </c>
       <c r="D35" s="5">
-        <f t="shared" si="0"/>
-        <v>83.331117900361363</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5">
-        <v>40.930159700825556</v>
-      </c>
-      <c r="C36" s="5">
-        <v>39.005627517921248</v>
-      </c>
-      <c r="D36" s="5">
-        <f t="shared" si="0"/>
-        <v>101.9245321829043</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5">
-        <v>52.850453128973712</v>
-      </c>
-      <c r="C37" s="5">
-        <v>40.797518650311957</v>
-      </c>
-      <c r="D37" s="5">
-        <f t="shared" si="0"/>
-        <v>112.05293447866175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5">
-        <v>45.450453128973713</v>
-      </c>
-      <c r="C38" s="5">
-        <v>37.024783770705895</v>
-      </c>
-      <c r="D38" s="5">
-        <f t="shared" si="0"/>
-        <v>108.42566935826781</v>
+        <f t="shared" si="1"/>
+        <v>113.45045312897372</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Control_Database.xlsx
+++ b/Data/Control_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7082DDAD-B45B-7D4E-9DD4-806BDE47EF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE85F46B-79D5-9E47-BE2B-CF8A52D9127C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13780" yWindow="1560" windowWidth="13620" windowHeight="16940" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>BRAND DATABASE</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Scale Score (Revenue)</t>
-  </si>
-  <si>
-    <t>Final Score</t>
   </si>
   <si>
     <t xml:space="preserve">GAP </t>
@@ -211,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -223,6 +220,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,489 +577,391 @@
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5">
-        <v>49.83383979741437</v>
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>43.3</v>
       </c>
       <c r="C4" s="6">
         <v>47</v>
       </c>
-      <c r="D4" s="5">
-        <f t="shared" ref="D4:D15" si="0">(B4-C4)+100</f>
-        <v>102.83383979741437</v>
-      </c>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5">
-        <v>54.234559509529525</v>
+        <v>6</v>
+      </c>
+      <c r="B5" s="7">
+        <v>43.3</v>
       </c>
       <c r="C5" s="6">
         <v>34</v>
       </c>
-      <c r="D5" s="5">
-        <f>(B5-C5)+100</f>
-        <v>120.23455950952953</v>
-      </c>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5">
-        <v>53.533759829401575</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>44.5</v>
       </c>
       <c r="C6" s="6">
         <v>66</v>
       </c>
-      <c r="D6" s="5">
-        <f>(B6-C6)+100</f>
-        <v>87.533759829401575</v>
-      </c>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5">
-        <v>39.60035985605758</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="7">
+        <v>34.1</v>
       </c>
       <c r="C7" s="6">
         <v>46</v>
       </c>
-      <c r="D7" s="5">
-        <f t="shared" si="0"/>
-        <v>93.60035985605758</v>
-      </c>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5">
-        <v>49.20095961615354</v>
+        <v>8</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45.9</v>
       </c>
       <c r="C8" s="6">
         <v>55</v>
       </c>
-      <c r="D8" s="5">
-        <f t="shared" si="0"/>
-        <v>94.20095961615354</v>
-      </c>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5">
-        <v>52.352872763937903</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>41.1</v>
       </c>
       <c r="C9" s="6">
         <v>100</v>
       </c>
-      <c r="D9" s="5">
-        <f t="shared" si="0"/>
-        <v>52.352872763937903</v>
-      </c>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="5">
-        <v>54.610314522371297</v>
+        <v>10</v>
+      </c>
+      <c r="B10" s="7">
+        <v>25.1</v>
       </c>
       <c r="C10" s="6">
         <v>55</v>
       </c>
-      <c r="D10" s="5">
-        <f t="shared" si="0"/>
-        <v>99.610314522371297</v>
-      </c>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="5">
-        <v>66.98073034217856</v>
+        <v>11</v>
+      </c>
+      <c r="B11" s="7">
+        <v>59.2</v>
       </c>
       <c r="C11" s="6">
         <v>71</v>
       </c>
-      <c r="D11" s="5">
-        <f t="shared" si="0"/>
-        <v>95.98073034217856</v>
-      </c>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="5">
-        <v>65.643346109831924</v>
+        <v>12</v>
+      </c>
+      <c r="B12" s="7">
+        <v>52.8</v>
       </c>
       <c r="C12" s="6">
         <v>67</v>
       </c>
-      <c r="D12" s="5">
-        <f t="shared" si="0"/>
-        <v>98.643346109831924</v>
-      </c>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5">
-        <v>59.415690964993317</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0</v>
       </c>
       <c r="C13" s="6">
         <v>50</v>
       </c>
-      <c r="D13" s="5">
-        <f t="shared" si="0"/>
-        <v>109.41569096499332</v>
-      </c>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="5">
-        <v>53.642262900429138</v>
+        <v>14</v>
+      </c>
+      <c r="B14" s="7">
+        <v>54.3</v>
       </c>
       <c r="C14" s="6">
         <v>59</v>
       </c>
-      <c r="D14" s="5">
-        <f t="shared" si="0"/>
-        <v>94.642262900429131</v>
-      </c>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5">
-        <v>60.395596306931772</v>
+        <v>15</v>
+      </c>
+      <c r="B15" s="7">
+        <v>29.6</v>
       </c>
       <c r="C15" s="6">
         <v>34</v>
       </c>
-      <c r="D15" s="5">
-        <f t="shared" si="0"/>
-        <v>126.39559630693176</v>
-      </c>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="5">
-        <v>57.96405074333903</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="7">
+        <v>44.3</v>
       </c>
       <c r="C16" s="6">
         <v>62</v>
       </c>
-      <c r="D16" s="5">
-        <f t="shared" ref="D16:D35" si="1">(B16-C16)+100</f>
-        <v>95.96405074333903</v>
-      </c>
+      <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="5">
-        <v>49.370522432274925</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="7">
+        <v>66.099999999999994</v>
       </c>
       <c r="C17" s="6">
         <v>53</v>
       </c>
-      <c r="D17" s="5">
-        <f t="shared" si="1"/>
-        <v>96.370522432274925</v>
-      </c>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="5">
-        <v>56.986668968776129</v>
+        <v>34</v>
+      </c>
+      <c r="B18" s="7">
+        <v>61.3</v>
       </c>
       <c r="C18" s="6">
         <v>49</v>
       </c>
-      <c r="D18" s="5">
-        <f t="shared" si="1"/>
-        <v>107.98666896877613</v>
-      </c>
+      <c r="D18" s="5"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5">
-        <v>57.911007555383392</v>
+        <v>17</v>
+      </c>
+      <c r="B19" s="7">
+        <v>22.9</v>
       </c>
       <c r="C19" s="6">
         <v>44</v>
       </c>
-      <c r="D19" s="5">
-        <f t="shared" si="1"/>
-        <v>113.91100755538339</v>
-      </c>
+      <c r="D19" s="5"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5">
-        <v>48.923577841590635</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="7">
+        <v>34.5</v>
       </c>
       <c r="C20" s="6">
         <v>57</v>
       </c>
-      <c r="D20" s="5">
-        <f t="shared" si="1"/>
-        <v>91.923577841590628</v>
-      </c>
+      <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="5">
-        <v>63</v>
+        <v>32</v>
+      </c>
+      <c r="B21" s="7">
+        <v>28.7</v>
       </c>
       <c r="C21" s="6">
         <v>24</v>
       </c>
-      <c r="D21" s="5">
-        <f t="shared" si="1"/>
-        <v>139</v>
-      </c>
+      <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5">
-        <v>61.593346109831927</v>
+        <v>19</v>
+      </c>
+      <c r="B22" s="7">
+        <v>34.700000000000003</v>
       </c>
       <c r="C22" s="6">
         <v>32</v>
       </c>
-      <c r="D22" s="5">
-        <f t="shared" si="1"/>
-        <v>129.59334610983194</v>
-      </c>
+      <c r="D22" s="5"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46.350059976009597</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="7">
+        <v>52.8</v>
       </c>
       <c r="C23" s="6">
         <v>47</v>
       </c>
-      <c r="D23" s="5">
-        <f t="shared" si="1"/>
-        <v>99.350059976009589</v>
-      </c>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="5">
-        <v>41.712159841945578</v>
+        <v>21</v>
+      </c>
+      <c r="B24" s="7">
+        <v>44</v>
       </c>
       <c r="C24" s="6">
         <v>59</v>
       </c>
-      <c r="D24" s="5">
-        <f t="shared" si="1"/>
-        <v>82.712159841945578</v>
-      </c>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="5">
-        <v>77.485759813721572</v>
+        <v>33</v>
+      </c>
+      <c r="B25" s="7">
+        <v>65.2</v>
       </c>
       <c r="C25" s="6">
         <v>48</v>
       </c>
-      <c r="D25" s="5">
-        <f t="shared" si="1"/>
-        <v>129.48575981372159</v>
-      </c>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="5">
-        <v>23.791959882713581</v>
+        <v>22</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0</v>
       </c>
       <c r="C26" s="6">
         <v>61</v>
       </c>
-      <c r="D26" s="5">
-        <f t="shared" si="1"/>
-        <v>62.791959882713584</v>
-      </c>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="5">
-        <v>47.849323850226448</v>
+        <v>23</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2.2999999999999998</v>
       </c>
       <c r="C27" s="6">
         <v>32</v>
       </c>
-      <c r="D27" s="5">
-        <f t="shared" si="1"/>
-        <v>115.84932385022645</v>
-      </c>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="5">
-        <v>60.95</v>
+        <v>24</v>
+      </c>
+      <c r="B28" s="7">
+        <v>51.5</v>
       </c>
       <c r="C28" s="6">
         <v>56</v>
       </c>
-      <c r="D28" s="5">
-        <f t="shared" si="1"/>
-        <v>104.95</v>
-      </c>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5">
-        <v>65.290591735576129</v>
+        <v>25</v>
+      </c>
+      <c r="B29" s="7">
+        <v>37.200000000000003</v>
       </c>
       <c r="C29" s="6">
         <v>29</v>
       </c>
-      <c r="D29" s="5">
-        <f t="shared" si="1"/>
-        <v>136.29059173557613</v>
-      </c>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="5">
-        <v>51.751839194997913</v>
+        <v>26</v>
+      </c>
+      <c r="B30" s="7">
+        <v>29.3</v>
       </c>
       <c r="C30" s="6">
         <v>13</v>
       </c>
-      <c r="D30" s="5">
-        <f t="shared" si="1"/>
-        <v>138.7518391949979</v>
-      </c>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="5">
-        <v>37.600733828705188</v>
+        <v>35</v>
+      </c>
+      <c r="B31" s="7">
+        <v>2.4</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
       </c>
-      <c r="D31" s="5">
-        <f t="shared" si="1"/>
-        <v>137.60073382870519</v>
-      </c>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="5">
-        <v>40.300959616153534</v>
+        <v>27</v>
+      </c>
+      <c r="B32" s="7">
+        <v>6.5</v>
       </c>
       <c r="C32" s="6">
         <v>25</v>
       </c>
-      <c r="D32" s="5">
-        <f t="shared" si="1"/>
-        <v>115.30095961615353</v>
-      </c>
+      <c r="D32" s="5"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="5">
-        <v>40.930159700825556</v>
+        <v>28</v>
+      </c>
+      <c r="B33" s="7">
+        <v>6.5</v>
       </c>
       <c r="C33" s="6">
         <v>39</v>
       </c>
-      <c r="D33" s="5">
-        <f t="shared" si="1"/>
-        <v>101.93015970082556</v>
-      </c>
+      <c r="D33" s="5"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="5">
-        <v>52.850453128973712</v>
+        <v>29</v>
+      </c>
+      <c r="B34" s="7">
+        <v>8.8000000000000007</v>
       </c>
       <c r="C34" s="6">
         <v>40</v>
       </c>
-      <c r="D34" s="5">
-        <f t="shared" si="1"/>
-        <v>112.85045312897371</v>
-      </c>
+      <c r="D34" s="5"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="5">
-        <v>45.450453128973713</v>
+        <v>30</v>
+      </c>
+      <c r="B35" s="7">
+        <v>5.7</v>
       </c>
       <c r="C35" s="6">
         <v>32</v>
       </c>
-      <c r="D35" s="5">
-        <f t="shared" si="1"/>
-        <v>113.45045312897372</v>
-      </c>
+      <c r="D35" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Control_Database.xlsx
+++ b/Data/Control_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE85F46B-79D5-9E47-BE2B-CF8A52D9127C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD00E23-19F3-244E-A3E3-864FFD1EF811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>BRAND DATABASE</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Brand</t>
   </si>
@@ -150,16 +147,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -208,19 +197,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,413 +543,407 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF1633F-6EA6-034C-A39E-6A5F71E344D2}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="B2" s="6">
+        <v>43.3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6">
+        <v>43.3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7">
-        <v>43.3</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="6">
+        <v>44.5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>66</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>34.1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6">
+        <v>45.9</v>
+      </c>
+      <c r="C6" s="5">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6">
+        <v>41.1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6">
+        <v>25.1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>55</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6">
+        <v>59.2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>71</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="6">
+        <v>52.8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>67</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="6">
+        <v>54.3</v>
+      </c>
+      <c r="C12" s="5">
+        <v>59</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="6">
+        <v>29.6</v>
+      </c>
+      <c r="C13" s="5">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6">
+        <v>44.3</v>
+      </c>
+      <c r="C14" s="5">
+        <v>62</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="6">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C15" s="5">
+        <v>53</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="6">
+        <v>61.3</v>
+      </c>
+      <c r="C16" s="5">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="C17" s="5">
+        <v>44</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>34.5</v>
+      </c>
+      <c r="C18" s="5">
+        <v>57</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="6">
+        <v>28.7</v>
+      </c>
+      <c r="C19" s="5">
+        <v>24</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="C20" s="5">
+        <v>32</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6">
+        <v>52.8</v>
+      </c>
+      <c r="C21" s="5">
         <v>47</v>
       </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="7">
-        <v>43.3</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>44</v>
+      </c>
+      <c r="C22" s="5">
+        <v>59</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="6">
+        <v>65.2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>48</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5">
+        <v>61</v>
+      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C25" s="5">
+        <v>32</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6">
+        <v>51.5</v>
+      </c>
+      <c r="C26" s="5">
+        <v>56</v>
+      </c>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="C27" s="5">
+        <v>29</v>
+      </c>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6">
+        <v>29.3</v>
+      </c>
+      <c r="C28" s="5">
+        <v>13</v>
+      </c>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>44.5</v>
-      </c>
-      <c r="C6" s="6">
-        <v>66</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7">
-        <v>34.1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>46</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="7">
-        <v>45.9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>55</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7">
-        <v>41.1</v>
-      </c>
-      <c r="C9" s="6">
-        <v>100</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="7">
-        <v>25.1</v>
-      </c>
-      <c r="C10" s="6">
-        <v>55</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="7">
-        <v>59.2</v>
-      </c>
-      <c r="C11" s="6">
-        <v>71</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="7">
-        <v>52.8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>67</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="7">
+      <c r="B29" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="C29" s="5">
         <v>0</v>
       </c>
-      <c r="C13" s="6">
-        <v>50</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="7">
-        <v>54.3</v>
-      </c>
-      <c r="C14" s="6">
-        <v>59</v>
-      </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="7">
-        <v>29.6</v>
-      </c>
-      <c r="C15" s="6">
-        <v>34</v>
-      </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="7">
-        <v>44.3</v>
-      </c>
-      <c r="C16" s="6">
-        <v>62</v>
-      </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="C17" s="6">
-        <v>53</v>
-      </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="7">
-        <v>61.3</v>
-      </c>
-      <c r="C18" s="6">
-        <v>49</v>
-      </c>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="7">
-        <v>22.9</v>
-      </c>
-      <c r="C19" s="6">
-        <v>44</v>
-      </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7">
-        <v>34.5</v>
-      </c>
-      <c r="C20" s="6">
-        <v>57</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="C30" s="5">
+        <v>25</v>
+      </c>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="C31" s="5">
+        <v>39</v>
+      </c>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="C32" s="5">
+        <v>40</v>
+      </c>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="C33" s="5">
         <v>32</v>
       </c>
-      <c r="B21" s="7">
-        <v>28.7</v>
-      </c>
-      <c r="C21" s="6">
-        <v>24</v>
-      </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="C22" s="6">
-        <v>32</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="7">
-        <v>52.8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>47</v>
-      </c>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7">
-        <v>44</v>
-      </c>
-      <c r="C24" s="6">
-        <v>59</v>
-      </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7">
-        <v>65.2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>48</v>
-      </c>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="7">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6">
-        <v>61</v>
-      </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="7">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C27" s="6">
-        <v>32</v>
-      </c>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="7">
-        <v>51.5</v>
-      </c>
-      <c r="C28" s="6">
-        <v>56</v>
-      </c>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="7">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="C29" s="6">
-        <v>29</v>
-      </c>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="7">
-        <v>29.3</v>
-      </c>
-      <c r="C30" s="6">
-        <v>13</v>
-      </c>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0</v>
-      </c>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="C32" s="6">
-        <v>25</v>
-      </c>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="C33" s="6">
-        <v>39</v>
-      </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="7">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="C34" s="6">
-        <v>40</v>
-      </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="7">
-        <v>5.7</v>
-      </c>
-      <c r="C35" s="6">
-        <v>32</v>
-      </c>
-      <c r="D35" s="5"/>
+      <c r="D33" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Control_Database.xlsx
+++ b/Data/Control_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD00E23-19F3-244E-A3E3-864FFD1EF811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C015A-708D-644B-94D0-7E59C6864628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Brand</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Under Armour</t>
   </si>
   <si>
-    <t>Lululemon</t>
-  </si>
-  <si>
     <t>New Balance</t>
   </si>
   <si>
@@ -128,12 +125,6 @@
     <t xml:space="preserve">LL Bean </t>
   </si>
   <si>
-    <t>Ralph Lauren Corporation</t>
-  </si>
-  <si>
-    <t>Kate Spade &amp; Co</t>
-  </si>
-  <si>
     <t>The North Face</t>
   </si>
   <si>
@@ -141,6 +132,12 @@
   </si>
   <si>
     <t>Tom Ford</t>
+  </si>
+  <si>
+    <t>Kate Spade &amp; Co.</t>
+  </si>
+  <si>
+    <t>Ralph Lauren</t>
   </si>
 </sst>
 </file>
@@ -650,10 +647,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="6">
-        <v>59.2</v>
+        <v>52.8</v>
       </c>
       <c r="C9" s="5">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D9" s="4"/>
     </row>
@@ -662,10 +659,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="6">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D10" s="4"/>
     </row>
@@ -674,10 +671,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="6">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="C11" s="5">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D11" s="4"/>
     </row>
@@ -686,58 +683,58 @@
         <v>13</v>
       </c>
       <c r="B12" s="6">
-        <v>54.3</v>
+        <v>29.6</v>
       </c>
       <c r="C12" s="5">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
-        <v>29.6</v>
+        <v>44.3</v>
       </c>
       <c r="C13" s="5">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B14" s="6">
-        <v>44.3</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="C14" s="5">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B15" s="6">
-        <v>66.099999999999994</v>
+        <v>61.3</v>
       </c>
       <c r="C15" s="5">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6">
-        <v>61.3</v>
+        <v>22.9</v>
       </c>
       <c r="C16" s="5">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -746,34 +743,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="6">
-        <v>22.9</v>
+        <v>34.5</v>
       </c>
       <c r="C17" s="5">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6">
-        <v>34.5</v>
+        <v>28.7</v>
       </c>
       <c r="C18" s="5">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B19" s="6">
-        <v>28.7</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="C19" s="5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D19" s="4"/>
     </row>
@@ -782,10 +779,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="6">
-        <v>34.700000000000003</v>
+        <v>52.8</v>
       </c>
       <c r="C20" s="5">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D20" s="4"/>
     </row>
@@ -794,34 +791,34 @@
         <v>19</v>
       </c>
       <c r="B21" s="6">
-        <v>52.8</v>
+        <v>44</v>
       </c>
       <c r="C21" s="5">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B22" s="6">
-        <v>44</v>
+        <v>65.2</v>
       </c>
       <c r="C22" s="5">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B23" s="6">
-        <v>65.2</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D23" s="4"/>
     </row>
@@ -830,10 +827,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="6">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C24" s="5">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D24" s="4"/>
     </row>
@@ -842,10 +839,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="6">
-        <v>2.2999999999999998</v>
+        <v>51.5</v>
       </c>
       <c r="C25" s="5">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4"/>
     </row>
@@ -854,10 +851,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="6">
-        <v>51.5</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="C26" s="5">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D26" s="4"/>
     </row>
@@ -866,34 +863,34 @@
         <v>24</v>
       </c>
       <c r="B27" s="6">
-        <v>37.200000000000003</v>
+        <v>29.3</v>
       </c>
       <c r="C27" s="5">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D27" s="4"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B28" s="6">
-        <v>29.3</v>
+        <v>2.4</v>
       </c>
       <c r="C28" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D28" s="4"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="C29" s="5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D29" s="4"/>
     </row>
@@ -905,7 +902,7 @@
         <v>6.5</v>
       </c>
       <c r="C30" s="5">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D30" s="4"/>
     </row>
@@ -914,10 +911,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <v>6.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C31" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D31" s="4"/>
     </row>
@@ -926,23 +923,14 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <v>8.8000000000000007</v>
+        <v>5.7</v>
       </c>
       <c r="C32" s="5">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="C33" s="5">
-        <v>32</v>
-      </c>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D33" s="4"/>
     </row>
   </sheetData>

--- a/Data/Control_Database.xlsx
+++ b/Data/Control_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C015A-708D-644B-94D0-7E59C6864628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5C2664-ABF3-2446-B603-E6AC34879C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
   </bookViews>
@@ -194,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -205,7 +205,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,8 +561,8 @@
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6">
-        <v>43.3</v>
+      <c r="B2" s="5">
+        <v>43</v>
       </c>
       <c r="C2" s="5">
         <v>47</v>
@@ -574,8 +573,8 @@
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6">
-        <v>43.3</v>
+      <c r="B3" s="5">
+        <v>43</v>
       </c>
       <c r="C3" s="5">
         <v>34</v>
@@ -586,8 +585,8 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
-        <v>44.5</v>
+      <c r="B4" s="5">
+        <v>53</v>
       </c>
       <c r="C4" s="5">
         <v>66</v>
@@ -598,8 +597,8 @@
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6">
-        <v>34.1</v>
+      <c r="B5" s="5">
+        <v>36</v>
       </c>
       <c r="C5" s="5">
         <v>46</v>
@@ -610,8 +609,8 @@
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6">
-        <v>45.9</v>
+      <c r="B6" s="5">
+        <v>50</v>
       </c>
       <c r="C6" s="5">
         <v>55</v>
@@ -622,8 +621,8 @@
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6">
-        <v>41.1</v>
+      <c r="B7" s="5">
+        <v>49</v>
       </c>
       <c r="C7" s="5">
         <v>100</v>
@@ -634,8 +633,8 @@
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6">
-        <v>25.1</v>
+      <c r="B8" s="5">
+        <v>34</v>
       </c>
       <c r="C8" s="5">
         <v>55</v>
@@ -646,8 +645,8 @@
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="6">
-        <v>52.8</v>
+      <c r="B9" s="5">
+        <v>53</v>
       </c>
       <c r="C9" s="5">
         <v>67</v>
@@ -658,8 +657,8 @@
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6">
-        <v>0</v>
+      <c r="B10" s="5">
+        <v>13</v>
       </c>
       <c r="C10" s="5">
         <v>50</v>
@@ -670,8 +669,8 @@
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6">
-        <v>54.3</v>
+      <c r="B11" s="5">
+        <v>55</v>
       </c>
       <c r="C11" s="5">
         <v>59</v>
@@ -682,8 +681,8 @@
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="6">
-        <v>29.6</v>
+      <c r="B12" s="5">
+        <v>40</v>
       </c>
       <c r="C12" s="5">
         <v>34</v>
@@ -694,8 +693,8 @@
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="6">
-        <v>44.3</v>
+      <c r="B13" s="5">
+        <v>59</v>
       </c>
       <c r="C13" s="5">
         <v>62</v>
@@ -706,8 +705,8 @@
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="6">
-        <v>66.099999999999994</v>
+      <c r="B14" s="5">
+        <v>61</v>
       </c>
       <c r="C14" s="5">
         <v>53</v>
@@ -718,8 +717,8 @@
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="6">
-        <v>61.3</v>
+      <c r="B15" s="5">
+        <v>56</v>
       </c>
       <c r="C15" s="5">
         <v>49</v>
@@ -730,8 +729,8 @@
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
-        <v>22.9</v>
+      <c r="B16" s="5">
+        <v>29</v>
       </c>
       <c r="C16" s="5">
         <v>44</v>
@@ -742,8 +741,8 @@
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
-        <v>34.5</v>
+      <c r="B17" s="5">
+        <v>44</v>
       </c>
       <c r="C17" s="5">
         <v>57</v>
@@ -754,8 +753,8 @@
       <c r="A18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="6">
-        <v>28.7</v>
+      <c r="B18" s="5">
+        <v>45</v>
       </c>
       <c r="C18" s="5">
         <v>24</v>
@@ -766,8 +765,8 @@
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="6">
-        <v>34.700000000000003</v>
+      <c r="B19" s="5">
+        <v>56</v>
       </c>
       <c r="C19" s="5">
         <v>32</v>
@@ -778,8 +777,8 @@
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="6">
-        <v>52.8</v>
+      <c r="B20" s="5">
+        <v>52</v>
       </c>
       <c r="C20" s="5">
         <v>47</v>
@@ -790,8 +789,8 @@
       <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="6">
-        <v>44</v>
+      <c r="B21" s="5">
+        <v>41</v>
       </c>
       <c r="C21" s="5">
         <v>59</v>
@@ -802,8 +801,8 @@
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="6">
-        <v>65.2</v>
+      <c r="B22" s="5">
+        <v>59</v>
       </c>
       <c r="C22" s="5">
         <v>48</v>
@@ -814,8 +813,8 @@
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
+      <c r="B23" s="5">
+        <v>15</v>
       </c>
       <c r="C23" s="5">
         <v>61</v>
@@ -826,8 +825,8 @@
       <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="6">
-        <v>2.2999999999999998</v>
+      <c r="B24" s="5">
+        <v>20</v>
       </c>
       <c r="C24" s="5">
         <v>32</v>
@@ -838,8 +837,8 @@
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="6">
-        <v>51.5</v>
+      <c r="B25" s="5">
+        <v>54</v>
       </c>
       <c r="C25" s="5">
         <v>56</v>
@@ -850,8 +849,8 @@
       <c r="A26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="6">
-        <v>37.200000000000003</v>
+      <c r="B26" s="5">
+        <v>47</v>
       </c>
       <c r="C26" s="5">
         <v>29</v>
@@ -862,8 +861,8 @@
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="6">
-        <v>29.3</v>
+      <c r="B27" s="5">
+        <v>36</v>
       </c>
       <c r="C27" s="5">
         <v>13</v>
@@ -874,8 +873,8 @@
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="6">
-        <v>2.4</v>
+      <c r="B28" s="5">
+        <v>28</v>
       </c>
       <c r="C28" s="5">
         <v>0</v>
@@ -886,8 +885,8 @@
       <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="6">
-        <v>6.5</v>
+      <c r="B29" s="5">
+        <v>19</v>
       </c>
       <c r="C29" s="5">
         <v>25</v>
@@ -898,8 +897,8 @@
       <c r="A30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="6">
-        <v>6.5</v>
+      <c r="B30" s="5">
+        <v>25</v>
       </c>
       <c r="C30" s="5">
         <v>39</v>
@@ -910,8 +909,8 @@
       <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="6">
-        <v>8.8000000000000007</v>
+      <c r="B31" s="5">
+        <v>22</v>
       </c>
       <c r="C31" s="5">
         <v>40</v>
@@ -922,8 +921,8 @@
       <c r="A32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="6">
-        <v>5.7</v>
+      <c r="B32" s="5">
+        <v>19</v>
       </c>
       <c r="C32" s="5">
         <v>32</v>

--- a/Data/Control_Database.xlsx
+++ b/Data/Control_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablopadres/Documents/School/MS2/thesis/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5C2664-ABF3-2446-B603-E6AC34879C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E10F38-E066-554A-8F45-A4017737FA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="11740" windowHeight="17740" xr2:uid="{B3FEFE8E-EE57-4347-946A-85911BAAFB0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -173,6 +173,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -194,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -205,6 +212,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,8 +569,8 @@
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5">
-        <v>43</v>
+      <c r="B2" s="6">
+        <v>43.902000000000001</v>
       </c>
       <c r="C2" s="5">
         <v>47</v>
@@ -573,8 +581,8 @@
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5">
-        <v>43</v>
+      <c r="B3" s="6">
+        <v>43.902000000000001</v>
       </c>
       <c r="C3" s="5">
         <v>34</v>
@@ -585,8 +593,8 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
-        <v>53</v>
+      <c r="B4" s="6">
+        <v>53.701999999999998</v>
       </c>
       <c r="C4" s="5">
         <v>66</v>
@@ -597,8 +605,8 @@
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5">
-        <v>36</v>
+      <c r="B5" s="6">
+        <v>32.238</v>
       </c>
       <c r="C5" s="5">
         <v>46</v>
@@ -609,8 +617,8 @@
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5">
-        <v>50</v>
+      <c r="B6" s="6">
+        <v>47.842999999999996</v>
       </c>
       <c r="C6" s="5">
         <v>55</v>
@@ -621,8 +629,8 @@
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5">
-        <v>49</v>
+      <c r="B7" s="6">
+        <v>51.3825</v>
       </c>
       <c r="C7" s="5">
         <v>100</v>
@@ -633,8 +641,8 @@
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5">
-        <v>34</v>
+      <c r="B8" s="6">
+        <v>38.596999999999994</v>
       </c>
       <c r="C8" s="5">
         <v>55</v>
@@ -645,8 +653,8 @@
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5">
-        <v>53</v>
+      <c r="B9" s="6">
+        <v>51.706499999999991</v>
       </c>
       <c r="C9" s="5">
         <v>67</v>
@@ -657,8 +665,8 @@
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5">
-        <v>13</v>
+      <c r="B10" s="6">
+        <v>16.338000000000001</v>
       </c>
       <c r="C10" s="5">
         <v>50</v>
@@ -669,8 +677,8 @@
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5">
-        <v>55</v>
+      <c r="B11" s="6">
+        <v>48.638000000000005</v>
       </c>
       <c r="C11" s="5">
         <v>59</v>
@@ -681,8 +689,8 @@
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5">
-        <v>40</v>
+      <c r="B12" s="6">
+        <v>43.695</v>
       </c>
       <c r="C12" s="5">
         <v>34</v>
@@ -693,8 +701,8 @@
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="5">
-        <v>59</v>
+      <c r="B13" s="6">
+        <v>62.688499999999998</v>
       </c>
       <c r="C13" s="5">
         <v>62</v>
@@ -705,8 +713,8 @@
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5">
-        <v>61</v>
+      <c r="B14" s="6">
+        <v>57.501000000000005</v>
       </c>
       <c r="C14" s="5">
         <v>53</v>
@@ -717,8 +725,8 @@
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="5">
-        <v>56</v>
+      <c r="B15" s="6">
+        <v>54.700999999999993</v>
       </c>
       <c r="C15" s="5">
         <v>49</v>
@@ -729,8 +737,8 @@
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
-        <v>29</v>
+      <c r="B16" s="6">
+        <v>29.988</v>
       </c>
       <c r="C16" s="5">
         <v>44</v>
@@ -741,8 +749,8 @@
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5">
-        <v>44</v>
+      <c r="B17" s="6">
+        <v>46.566500000000005</v>
       </c>
       <c r="C17" s="5">
         <v>57</v>
@@ -753,8 +761,8 @@
       <c r="A18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="5">
-        <v>45</v>
+      <c r="B18" s="6">
+        <v>48.966499999999996</v>
       </c>
       <c r="C18" s="5">
         <v>24</v>
@@ -765,8 +773,8 @@
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5">
-        <v>56</v>
+      <c r="B19" s="6">
+        <v>58.982499999999995</v>
       </c>
       <c r="C19" s="5">
         <v>32</v>
@@ -777,8 +785,8 @@
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="5">
-        <v>52</v>
+      <c r="B20" s="6">
+        <v>52.933</v>
       </c>
       <c r="C20" s="5">
         <v>47</v>
@@ -789,8 +797,8 @@
       <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="5">
-        <v>41</v>
+      <c r="B21" s="6">
+        <v>38.291499999999999</v>
       </c>
       <c r="C21" s="5">
         <v>59</v>
@@ -801,8 +809,8 @@
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="5">
-        <v>59</v>
+      <c r="B22" s="6">
+        <v>58.433500000000002</v>
       </c>
       <c r="C22" s="5">
         <v>48</v>
@@ -813,8 +821,8 @@
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="5">
-        <v>15</v>
+      <c r="B23" s="6">
+        <v>18.338000000000001</v>
       </c>
       <c r="C23" s="5">
         <v>61</v>
@@ -825,8 +833,8 @@
       <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="5">
-        <v>20</v>
+      <c r="B24" s="6">
+        <v>23.238000000000003</v>
       </c>
       <c r="C24" s="5">
         <v>32</v>
@@ -837,8 +845,8 @@
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="5">
-        <v>54</v>
+      <c r="B25" s="6">
+        <v>54.53</v>
       </c>
       <c r="C25" s="5">
         <v>56</v>
@@ -849,8 +857,8 @@
       <c r="A26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="5">
-        <v>47</v>
+      <c r="B26" s="6">
+        <v>48.365000000000002</v>
       </c>
       <c r="C26" s="5">
         <v>29</v>
@@ -861,8 +869,8 @@
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="5">
-        <v>36</v>
+      <c r="B27" s="6">
+        <v>35.137999999999998</v>
       </c>
       <c r="C27" s="5">
         <v>13</v>
@@ -873,8 +881,8 @@
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="5">
-        <v>28</v>
+      <c r="B28" s="6">
+        <v>42.613500000000002</v>
       </c>
       <c r="C28" s="5">
         <v>0</v>
@@ -885,8 +893,8 @@
       <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="5">
-        <v>19</v>
+      <c r="B29" s="6">
+        <v>22.038</v>
       </c>
       <c r="C29" s="5">
         <v>25</v>
@@ -897,8 +905,8 @@
       <c r="A30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="5">
-        <v>25</v>
+      <c r="B30" s="6">
+        <v>27.637999999999998</v>
       </c>
       <c r="C30" s="5">
         <v>39</v>
@@ -909,8 +917,8 @@
       <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="5">
-        <v>22</v>
+      <c r="B31" s="6">
+        <v>24.238000000000003</v>
       </c>
       <c r="C31" s="5">
         <v>40</v>
@@ -921,8 +929,8 @@
       <c r="A32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="5">
-        <v>19</v>
+      <c r="B32" s="6">
+        <v>20.938000000000002</v>
       </c>
       <c r="C32" s="5">
         <v>32</v>
